--- a/artfynd/A 67603-2021 artfynd.xlsx
+++ b/artfynd/A 67603-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 67603-2021 artfynd.xlsx
+++ b/artfynd/A 67603-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68043154</v>
+        <v>62058471</v>
       </c>
       <c r="B2" t="n">
-        <v>76579</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4202</v>
+        <v>1818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Småfruktigt blågryn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geoglossum umbratile</t>
+          <t>Gregorella humida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sacc.</t>
+          <t>(Kullh.) Lumbsch</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Roxtorp, Ög</t>
+          <t>Roxtorp täkt, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509386.8023306759</v>
+        <v>509350</v>
       </c>
       <c r="R2" t="n">
-        <v>6467704.851010459</v>
+        <v>6467725</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-09-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-10-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,13 +756,9 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Sandig kalkmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,15 +779,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68043155</v>
+        <v>68043157</v>
       </c>
       <c r="B3" t="n">
-        <v>76567</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +790,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4194</v>
+        <v>3296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattad jordtunga</t>
+          <t>Gullfingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geoglossum cookeianum</t>
+          <t>Clavulinopsis laeticolor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nannf.</t>
+          <t>(Berk. &amp; M.A.Curtis) R.H.Petersen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509384.18211702</v>
+        <v>509333</v>
       </c>
       <c r="R3" t="n">
-        <v>6467701.171011931</v>
+        <v>6467714</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,27 +847,18 @@
           <t>2017-09-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-10-19</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -917,64 +886,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6835814</v>
+        <v>68043155</v>
       </c>
       <c r="B4" t="n">
-        <v>98539</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>83320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224913</v>
+        <v>4194</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Plattad jordtunga</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>Geoglossum cookeanum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Minter &amp; P.F.Cannon</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra Lärketorp, Ög</t>
+          <t>Roxtorp, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509415.8250554011</v>
+        <v>509384</v>
       </c>
       <c r="R4" t="n">
-        <v>6467661.359799324</v>
+        <v>6467701</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,27 +951,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-06-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-06-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ungefärligt antal plantor.</t>
+          <t>2017-10-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,21 +970,467 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Skogsbryn</t>
+          <t>Sandig kalkmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÅGP stäppfingersvamp Östergötland </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>68043158</v>
+      </c>
+      <c r="B5" t="n">
+        <v>83320</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4194</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Plattad jordtunga</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Geoglossum cookeanum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Minter &amp; P.F.Cannon</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Roxtorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>509324</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6467728</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mjölby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Högby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-10-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Sandig kalkmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÅGP stäppfingersvamp Östergötland </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>68043154</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83330</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart jordtunga</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Geoglossum umbratile</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sacc.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Roxtorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>509387</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6467705</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mjölby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Högby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-09-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-10-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Sandig kalkmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÅGP stäppfingersvamp Östergötland </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6331783</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101348</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>224913</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig backsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Karlslund, 190 m V, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>509394</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6467673</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mjölby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Högby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2011-05-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2011-05-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Vägkant/bryn mot f d täkt</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tommy Karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tommy Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6835814</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101348</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>224913</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig backsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Östra Lärketorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>509416</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6467661</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mjölby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Högby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2013-06-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2013-06-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ungefärligt antal plantor.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Skogsbryn</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Bengt Westman</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Bengt Westman</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 67603-2021 artfynd.xlsx
+++ b/artfynd/A 67603-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
           <t xml:space="preserve">ÅGP stäppfingersvamp Östergötland </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62058471</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
           <t xml:space="preserve">ÅGP stäppfingersvamp Östergötland </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68043157</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
           <t xml:space="preserve">ÅGP stäppfingersvamp Östergötland </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68043155</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
           <t xml:space="preserve">ÅGP stäppfingersvamp Östergötland </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68043158</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
           <t xml:space="preserve">ÅGP stäppfingersvamp Östergötland </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68043154</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6331783</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,8 +1466,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6835814</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>